--- a/Practice Excel File.xlsx
+++ b/Practice Excel File.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cadd Mentor\Student_Class_Code\Siddhi_Vinayak_Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B636B7D-0B57-4396-845A-BA957B55CFC2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BA532C9-BC23-4F2D-8EA7-A2A27D283A25}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" firstSheet="3" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,21 @@
     <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
     <sheet name="Sheet8" sheetId="8" r:id="rId6"/>
     <sheet name="Sheet9" sheetId="9" r:id="rId7"/>
+    <sheet name="Sheet6" sheetId="10" r:id="rId8"/>
+    <sheet name="Sheet7" sheetId="11" r:id="rId9"/>
+    <sheet name="Scenario Summary" sheetId="19" r:id="rId10"/>
+    <sheet name="Sheet15" sheetId="17" r:id="rId11"/>
+    <sheet name="Sheet10" sheetId="20" r:id="rId12"/>
+    <sheet name="Sheet11" sheetId="21" r:id="rId13"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Sheet9!$A$1:$D$9</definedName>
+    <definedName name="AC">Sheet7!$B$5</definedName>
+    <definedName name="Chair">Sheet7!$B$3</definedName>
+    <definedName name="NEWCHAIR">Sheet15!$B$3</definedName>
+    <definedName name="Table">Sheet7!$B$4</definedName>
+    <definedName name="Total">Sheet7!$B$7</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -31,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="102">
   <si>
     <t>Sr No.</t>
   </si>
@@ -220,17 +234,137 @@
   </si>
   <si>
     <t>Fee</t>
+  </si>
+  <si>
+    <t>Suman</t>
+  </si>
+  <si>
+    <t>Saurabh</t>
+  </si>
+  <si>
+    <t>Noida</t>
+  </si>
+  <si>
+    <t>Lucknow</t>
+  </si>
+  <si>
+    <t>Delhi</t>
+  </si>
+  <si>
+    <t>Himanshi</t>
+  </si>
+  <si>
+    <t>Saloni</t>
+  </si>
+  <si>
+    <t>Rekha</t>
+  </si>
+  <si>
+    <t>Mo Number</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Chair</t>
+  </si>
+  <si>
+    <t>Table</t>
+  </si>
+  <si>
+    <t>AC</t>
+  </si>
+  <si>
+    <t>$C$3</t>
+  </si>
+  <si>
+    <t>$C$4</t>
+  </si>
+  <si>
+    <t>$C$5</t>
+  </si>
+  <si>
+    <t>$C$7</t>
+  </si>
+  <si>
+    <t>Created by pc on 30-03-2026</t>
+  </si>
+  <si>
+    <t>Scenario Summary</t>
+  </si>
+  <si>
+    <t>Changing Cells:</t>
+  </si>
+  <si>
+    <t>Current Values:</t>
+  </si>
+  <si>
+    <t>Result Cells:</t>
+  </si>
+  <si>
+    <t>Notes:  Current Values column represents values of changing cells at</t>
+  </si>
+  <si>
+    <t>time Scenario Summary Report was created.  Changing cells for each</t>
+  </si>
+  <si>
+    <t>scenario are highlighted in gray.</t>
+  </si>
+  <si>
+    <t>CHAIR</t>
+  </si>
+  <si>
+    <t>TABLE</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>SHOP1</t>
+  </si>
+  <si>
+    <t>SHOP2</t>
+  </si>
+  <si>
+    <t>AMMOUNT</t>
+  </si>
+  <si>
+    <t>RATE</t>
+  </si>
+  <si>
+    <t>MONTHS</t>
+  </si>
+  <si>
+    <t>EMI/MONTH</t>
+  </si>
+  <si>
+    <t>Interest</t>
+  </si>
+  <si>
+    <t>Sidhhi Vinayak Group Of Inst.</t>
+  </si>
+  <si>
+    <t>Sub1</t>
+  </si>
+  <si>
+    <t>Sub2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="5">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="168" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="169" formatCode="m/d/yy;@"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -289,8 +423,53 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="18"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -321,8 +500,26 @@
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="20"/>
+        <bgColor indexed="24"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="22"/>
+        <bgColor indexed="24"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="22"/>
+        <bgColor indexed="7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -341,12 +538,52 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -365,10 +602,52 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="12" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="4">
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{590ED08B-90BE-462C-A385-24608B6AB586}"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -848,6 +1127,373 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60F3A9E9-8826-42EF-8064-D2600141547C}">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="B1:F13"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="13.109375" bestFit="1" customWidth="1" outlineLevel="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="17"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+    </row>
+    <row r="3" spans="2:6" ht="15.6" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="F3" s="23" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="20.399999999999999" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="F4" s="25" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B5" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="20"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+    </row>
+    <row r="6" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="19"/>
+      <c r="C6" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" s="14">
+        <v>200</v>
+      </c>
+      <c r="E6" s="24">
+        <v>400</v>
+      </c>
+      <c r="F6" s="24">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="19"/>
+      <c r="C7" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="14">
+        <v>300</v>
+      </c>
+      <c r="E7" s="24">
+        <v>600</v>
+      </c>
+      <c r="F7" s="24">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="19"/>
+      <c r="C8" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" s="14">
+        <v>400</v>
+      </c>
+      <c r="E8" s="24">
+        <v>900</v>
+      </c>
+      <c r="F8" s="24">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B9" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="20"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+    </row>
+    <row r="10" spans="2:6" ht="15" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="21"/>
+      <c r="C10" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D10" s="15">
+        <v>900</v>
+      </c>
+      <c r="E10" s="15">
+        <v>1900</v>
+      </c>
+      <c r="F10" s="15">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7EE070E-D056-439F-88FE-A2B3F3087357}">
+  <dimension ref="B3:C7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7">
+        <f>SUM(C3:C5)</f>
+        <v>900</v>
+      </c>
+    </row>
+  </sheetData>
+  <scenarios current="0" sqref="C7">
+    <scenario name="SHOP1" locked="1" count="3" user="pc" comment="Created by pc on 30-03-2026">
+      <inputCells r="C3" val="400"/>
+      <inputCells r="C4" val="600"/>
+      <inputCells r="C5" val="900"/>
+    </scenario>
+    <scenario name="SHOP2" locked="1" count="3" user="pc" comment="Created by pc on 30-03-2026">
+      <inputCells r="C3" val="1200"/>
+      <inputCells r="C4" val="1300"/>
+      <inputCells r="C5" val="1500"/>
+    </scenario>
+  </scenarios>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A27E0FD-E85D-4AE3-B334-1EBAD0EB85CB}">
+  <dimension ref="C3:G12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="12.44140625" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+    </row>
+    <row r="4" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D4">
+        <v>500000</v>
+      </c>
+      <c r="F4" s="26"/>
+      <c r="G4" s="27"/>
+    </row>
+    <row r="5" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D5" s="26">
+        <v>0.12</v>
+      </c>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+    </row>
+    <row r="6" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6">
+        <v>60</v>
+      </c>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+    </row>
+    <row r="7" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+    </row>
+    <row r="8" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="D8" s="29">
+        <f>PMT(D5/12,D6,-D4)</f>
+        <v>11122.223842450885</v>
+      </c>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+    </row>
+    <row r="10" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" s="29">
+        <f>PMT(D5/12,D6,-D4)</f>
+        <v>11122.223842450885</v>
+      </c>
+    </row>
+    <row r="11" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C11" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" s="29">
+        <f>D10*D6</f>
+        <v>667333.43054705311</v>
+      </c>
+    </row>
+    <row r="12" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C12" t="s">
+        <v>98</v>
+      </c>
+      <c r="D12" s="29">
+        <f>D11-D4</f>
+        <v>167333.43054705311</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{506AB863-1B27-4620-96F2-98FA2B0D3DA9}">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="16.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="28"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B3" s="34"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="28"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4" s="33"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="28"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B5" s="28"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="28"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B6" s="28"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="28"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N9"/>
@@ -1197,6 +1843,14 @@
       <c r="D2">
         <v>22</v>
       </c>
+      <c r="E2">
+        <f>SUM(B2:D2)</f>
+        <v>145</v>
+      </c>
+      <c r="F2" t="str">
+        <f>IF(E2&gt;150,"PASS","FAIL")</f>
+        <v>FAIL</v>
+      </c>
       <c r="G2" s="12"/>
       <c r="H2" s="12"/>
     </row>
@@ -1213,6 +1867,13 @@
       <c r="D3">
         <v>49</v>
       </c>
+      <c r="E3">
+        <v>176</v>
+      </c>
+      <c r="F3" t="str">
+        <f t="shared" ref="F3:F4" si="0">IF(E3&gt;150,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
       <c r="G3" s="12"/>
       <c r="H3" s="12"/>
     </row>
@@ -1228,6 +1889,14 @@
       </c>
       <c r="D4">
         <v>89</v>
+      </c>
+      <c r="E4">
+        <f t="shared" ref="E3:E4" si="1">SUM(B4:D4)</f>
+        <v>178</v>
+      </c>
+      <c r="F4" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
       </c>
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
@@ -1354,13 +2023,14 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F955350B-35E3-49B5-828C-6B13C40D0DD1}">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="11.77734375" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
         <v>60</v>
       </c>
@@ -1372,9 +2042,247 @@
       </c>
       <c r="D1" s="13" t="s">
         <v>62</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>108</v>
+      </c>
+      <c r="B2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2">
+        <v>9000</v>
+      </c>
+      <c r="E2">
+        <v>1234567890</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>103</v>
+      </c>
+      <c r="B3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3">
+        <v>2000</v>
+      </c>
+      <c r="E3">
+        <v>1234567890</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>104</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4">
+        <v>5000</v>
+      </c>
+      <c r="E4">
+        <v>1234567890</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>107</v>
+      </c>
+      <c r="B5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5">
+        <v>4000</v>
+      </c>
+      <c r="E5">
+        <v>1234567890</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>102</v>
+      </c>
+      <c r="B6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6">
+        <v>4000</v>
+      </c>
+      <c r="E6">
+        <v>1234567890</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>106</v>
+      </c>
+      <c r="B7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7">
+        <v>2000</v>
+      </c>
+      <c r="E7">
+        <v>1234567890</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>105</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D8">
+        <v>8000</v>
+      </c>
+      <c r="E8">
+        <v>1234567890</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>101</v>
+      </c>
+      <c r="B9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9">
+        <v>2000</v>
+      </c>
+      <c r="E9">
+        <v>1234567890</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D9" xr:uid="{B81623AB-C056-44A8-98BA-A89EAABC5D8E}"/>
+  <sortState ref="A2:D9">
+    <sortCondition ref="C2:C9"/>
+  </sortState>
+  <dataValidations count="1">
+    <dataValidation type="textLength" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="This is is not acceptable" sqref="E2:E9" xr:uid="{1DCD5B03-F385-4ED7-883E-88E1A30C73D7}">
+      <formula1>10</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C20CA899-E0B7-4C66-8A44-215C96C10CBB}">
+  <dimension ref="B3:C6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6">
+        <f>C3*C4</f>
+        <v>25000</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85A29945-14B1-45EE-A01F-1A011B22243F}">
+  <dimension ref="B3:C7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <f>SUM(C3:C5)</f>
+        <v>1600</v>
+      </c>
+    </row>
+  </sheetData>
+  <scenarios current="0" sqref="C7">
+    <scenario name="Shop1" locked="1" count="3" user="pc" comment="Created by pc on 30-03-2026">
+      <inputCells r="C3" val="800"/>
+      <inputCells r="C4" val="1200"/>
+      <inputCells r="C5" val="1500"/>
+    </scenario>
+    <scenario name="Shop2" locked="1" count="3" user="pc" comment="Created by pc on 30-03-2026">
+      <inputCells r="C3" val="100"/>
+      <inputCells r="C4" val="200"/>
+      <inputCells r="C5" val="400"/>
+    </scenario>
+  </scenarios>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>